--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionCommentairePatient</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Encounter</t>
   </si>
   <si>
     <t>ID</t>
@@ -259,6 +259,9 @@
 </t>
   </si>
   <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -294,9 +297,6 @@
   <si>
     <t xml:space="preserve">Extension
 </t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -847,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -907,10 +907,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,7 +932,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -944,13 +944,13 @@
         <v>77</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1001,13 +1001,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1016,15 +1016,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1047,13 +1047,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1116,7 +1116,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1135,10 +1135,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1212,10 +1212,10 @@
         <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1240,10 +1240,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1255,7 +1255,7 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>104</v>
@@ -1318,7 +1318,7 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionCommentairePatient</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -259,9 +259,6 @@
 </t>
   </si>
   <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -297,6 +294,9 @@
   <si>
     <t xml:space="preserve">Extension
 </t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -847,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -907,10 +907,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,25 +932,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1001,13 +1001,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1016,15 +1016,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1047,13 +1047,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1116,7 +1116,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1135,10 +1135,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1212,10 +1212,10 @@
         <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>104</v>
@@ -1318,7 +1318,7 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
+++ b/nmoreau/ig/StructureDefinition-encounter-patient-comment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
